--- a/agent_runs/manjidiwang/episodes/ep19/storyboard_index.xlsx
+++ b/agent_runs/manjidiwang/episodes/ep19/storyboard_index.xlsx
@@ -84,7 +84,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>大厦门前押送（，总时长：12秒，镜头数：4个）</t>
+          <t>大厦门前押送</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -132,7 +132,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>警车离去后的提醒（，总时长：12秒，镜头数：4个）</t>
+          <t>警车离去后的提醒</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -180,7 +180,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>常委会夺权宣布（，总时长：10秒，镜头数：5个）</t>
+          <t>常委会夺权宣布</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -228,7 +228,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>朱天和抗议被压下（，总时长：14秒，镜头数：4个）</t>
+          <t>朱天和抗议被压下</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -276,7 +276,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>书房里看清局面（，总时长：14秒，镜头数：4个）</t>
+          <t>书房里看清局面</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -324,7 +324,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>带毒的桃子（，总时长：13秒，镜头数：4个）</t>
+          <t>带毒的桃子</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
